--- a/CS297TeamParticipationRubric.xlsx
+++ b/CS297TeamParticipationRubric.xlsx
@@ -1,18 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/birdb/Projects/CS297-Repos/CS297-CourseMaterials/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1625C1B2-D2AC-2344-8042-F7F19DBD361C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView minimized="1" xWindow="9820" yWindow="6620" windowWidth="17320" windowHeight="11720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Rubric" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Score" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Rubric" sheetId="1" r:id="rId1"/>
+    <sheet name="Score" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -23,57 +39,53 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="14">
   <si>
-    <t xml:space="preserve">Team Participation Rubric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Possible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Participation with your team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git pull requests (1 per week)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User story hours completed (8 per week)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint meeting attendance (3 per sprint)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily Stand-ups (4 per week)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Team work sessions (4 per week)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hours worked (12 per week)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">You did a good job of contributing to the success your team's project! Here is the participation grade breakdown:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Points</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total (100 maximum)</t>
+    <t>Team Participation Rubric</t>
+  </si>
+  <si>
+    <t>Possible</t>
+  </si>
+  <si>
+    <t>Participation with your team</t>
+  </si>
+  <si>
+    <t>Git pull requests (1 per week)</t>
+  </si>
+  <si>
+    <t>User story hours completed (8 per week)</t>
+  </si>
+  <si>
+    <t>Sprint meeting attendance (3 per sprint)</t>
+  </si>
+  <si>
+    <t>Daily Stand-ups (4 per week)</t>
+  </si>
+  <si>
+    <t>Team work sessions (4 per week)</t>
+  </si>
+  <si>
+    <t>Hours worked (12 per week)</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>You did a good job of contributing to the success your team's project! Here is the participation grade breakdown:</t>
+  </si>
+  <si>
+    <t>Points</t>
+  </si>
+  <si>
+    <t>Stats</t>
+  </si>
+  <si>
+    <t>Total (100 maximum)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="@"/>
-  </numFmts>
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -82,22 +94,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri Light"/>
@@ -105,8 +102,8 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <i val="true"/>
+      <b/>
+      <i/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri Light"/>
@@ -121,7 +118,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -138,148 +135,104 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -311,7 +264,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -335,7 +288,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -395,268 +348,254 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="2.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="36.6"/>
+    <col min="1" max="1" width="9.6640625" customWidth="1"/>
+    <col min="2" max="2" width="2.1640625" customWidth="1"/>
+    <col min="3" max="3" width="36.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="5"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="D3" s="5"/>
+      <c r="E3" s="6"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
         <v>20</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
         <v>30</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="C6" s="0" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="C7" s="0" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="C8" s="0" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9">
         <v>20</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
-        <f aca="false">SUM(A4:A9)</f>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <f>SUM(A4:A9)</f>
         <v>100</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="3.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="36.6"/>
+    <col min="1" max="1" width="9.33203125" customWidth="1"/>
+    <col min="2" max="2" width="8.1640625" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="3.1640625" customWidth="1"/>
+    <col min="5" max="5" width="36.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
+    <row r="3" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
       <c r="F3" s="8"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-    </row>
-    <row r="5" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="2" t="s">
+      <c r="D5" s="4"/>
+      <c r="E5" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6">
         <v>20</v>
       </c>
-      <c r="B6" s="0" t="n">
-        <f aca="false">C6*2</f>
+      <c r="B6">
+        <f>C6*2</f>
         <v>20</v>
       </c>
-      <c r="C6" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" s="0" t="s">
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7">
         <v>30</v>
       </c>
-      <c r="B7" s="0" t="n">
-        <f aca="false">C7*3/8</f>
+      <c r="B7">
+        <f>C7*3/8</f>
         <v>30</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7">
         <v>80</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="B8" s="0" t="n">
-        <f aca="false">C8*2/3</f>
-        <v>10</v>
-      </c>
-      <c r="C8" s="0" t="n">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <f>C8*2/3</f>
+        <v>10</v>
+      </c>
+      <c r="C8">
         <v>15</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="B9" s="0" t="n">
-        <f aca="false">C9/4</f>
-        <v>10</v>
-      </c>
-      <c r="C9" s="0" t="n">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <f>C9/4</f>
+        <v>10</v>
+      </c>
+      <c r="C9">
         <v>40</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="B10" s="0" t="n">
-        <f aca="false">C10/4</f>
-        <v>10</v>
-      </c>
-      <c r="C10" s="0" t="n">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <f>C10/4</f>
+        <v>10</v>
+      </c>
+      <c r="C10">
         <v>40</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11">
         <v>20</v>
       </c>
-      <c r="B11" s="0" t="n">
-        <f aca="false">C11/6</f>
+      <c r="B11">
+        <f>C11/6</f>
         <v>20</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11">
         <v>120</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
-        <f aca="false">SUM(A6:A11)</f>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <f>SUM(A6:A11)</f>
         <v>100</v>
       </c>
-      <c r="B13" s="0" t="n">
-        <f aca="false">SUM(B6:B11)</f>
+      <c r="B13">
+        <f>SUM(B6:B11)</f>
         <v>100</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="7" t="s">
         <v>13</v>
       </c>
     </row>
@@ -664,12 +603,7 @@
   <mergeCells count="1">
     <mergeCell ref="A3:E4"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/CS297TeamParticipationRubric.xlsx
+++ b/CS297TeamParticipationRubric.xlsx
@@ -5,16 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/birdb/Projects/CS297-Repos/CS297-CourseMaterials/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/birdb/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1625C1B2-D2AC-2344-8042-F7F19DBD361C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC057C3-1E57-5848-98A2-1AFBDE6E7237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="9820" yWindow="6620" windowWidth="17320" windowHeight="11720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9820" yWindow="6620" windowWidth="17320" windowHeight="11720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rubric" sheetId="1" r:id="rId1"/>
     <sheet name="Score" sheetId="2" r:id="rId2"/>
+    <sheet name="Pro-rated" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
   <si>
     <t>Team Participation Rubric</t>
   </si>
@@ -79,6 +80,12 @@
   </si>
   <si>
     <t>Total (100 maximum)</t>
+  </si>
+  <si>
+    <t>Number of weeks:</t>
+  </si>
+  <si>
+    <t>Maximum:</t>
   </si>
 </sst>
 </file>
@@ -155,11 +162,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -167,6 +171,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -369,20 +377,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="19" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="6"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="5"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
@@ -437,7 +445,7 @@
         <f>SUM(A4:A9)</f>
         <v>100</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>9</v>
       </c>
     </row>
@@ -460,39 +468,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="8"/>
+      <c r="A3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="7"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
     </row>
     <row r="5" spans="1:6" ht="19" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="3" t="s">
+      <c r="D5" s="3"/>
+      <c r="E5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -595,7 +603,7 @@
         <f>SUM(B6:B11)</f>
         <v>100</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -606,4 +614,168 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CEC3DD8-09F2-6143-9874-27C8FC46431E}">
+  <dimension ref="A2:G13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="2.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="9">
+        <f>Score!A6/$C$2</f>
+        <v>2.8571428571428572</v>
+      </c>
+      <c r="B6" s="9">
+        <f>C6*2</f>
+        <v>2.8571428571428572</v>
+      </c>
+      <c r="C6" s="9">
+        <f>Score!C6/$C$2</f>
+        <v>1.4285714285714286</v>
+      </c>
+      <c r="E6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="9">
+        <f>Score!A7/$C$2</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="B7" s="9">
+        <f>C7*3/8</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="C7" s="9">
+        <f>Score!C7/$C$2</f>
+        <v>11.428571428571429</v>
+      </c>
+      <c r="E7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="9">
+        <f>Score!A8/$C$2</f>
+        <v>1.4285714285714286</v>
+      </c>
+      <c r="B8" s="9">
+        <f>C8*2/3</f>
+        <v>1.4285714285714286</v>
+      </c>
+      <c r="C8" s="9">
+        <f>Score!C8/$C$2</f>
+        <v>2.1428571428571428</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="9">
+        <f>Score!A9/$C$2</f>
+        <v>1.4285714285714286</v>
+      </c>
+      <c r="B9" s="9">
+        <f>C9/4</f>
+        <v>1.4285714285714286</v>
+      </c>
+      <c r="C9" s="9">
+        <f>Score!C9/$C$2</f>
+        <v>5.7142857142857144</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="9">
+        <f>Score!A10/$C$2</f>
+        <v>1.4285714285714286</v>
+      </c>
+      <c r="B10" s="9">
+        <f>C10/4</f>
+        <v>1.4285714285714286</v>
+      </c>
+      <c r="C10" s="9">
+        <f>Score!C10/$C$2</f>
+        <v>5.7142857142857144</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="9">
+        <f>Score!A11/$C$2</f>
+        <v>2.8571428571428572</v>
+      </c>
+      <c r="B11" s="9">
+        <f>C11/6</f>
+        <v>2.8571428571428572</v>
+      </c>
+      <c r="C11" s="9">
+        <f>Score!C11/$C$2</f>
+        <v>17.142857142857142</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="9">
+        <f>SUM(A6:A11)</f>
+        <v>14.285714285714286</v>
+      </c>
+      <c r="B13" s="9">
+        <f>SUM(B6:B11)</f>
+        <v>14.285714285714286</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="E13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="9">
+        <f>100/C2</f>
+        <v>14.285714285714286</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/CS297TeamParticipationRubric.xlsx
+++ b/CS297TeamParticipationRubric.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/birdb/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/birdb/Projects/CS297-Repos/CS297-CourseMaterials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC057C3-1E57-5848-98A2-1AFBDE6E7237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20B18F1-AAA2-B342-9322-CB576A6D4F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9820" yWindow="6620" windowWidth="17320" windowHeight="11720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="15">
   <si>
     <t>Team Participation Rubric</t>
   </si>
@@ -58,12 +58,6 @@
     <t>Sprint meeting attendance (3 per sprint)</t>
   </si>
   <si>
-    <t>Daily Stand-ups (4 per week)</t>
-  </si>
-  <si>
-    <t>Team work sessions (4 per week)</t>
-  </si>
-  <si>
     <t>Hours worked (12 per week)</t>
   </si>
   <si>
@@ -85,7 +79,10 @@
     <t>Number of weeks:</t>
   </si>
   <si>
-    <t>Maximum:</t>
+    <t>Team work sessions (2 per week)</t>
+  </si>
+  <si>
+    <t>Daily Stand-ups (2 per week)</t>
   </si>
 </sst>
 </file>
@@ -162,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -171,10 +168,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -421,7 +419,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -429,7 +427,7 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -437,7 +435,7 @@
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -446,7 +444,7 @@
         <v>100</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -473,31 +471,31 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
+      <c r="A3" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
       <c r="F3" s="7"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
     </row>
     <row r="5" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="2" t="s">
@@ -554,14 +552,14 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <f>C9/4</f>
+        <f>C9/2</f>
         <v>10</v>
       </c>
       <c r="C9">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -569,14 +567,14 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <f>C10/4</f>
+        <f>C10/2</f>
         <v>10</v>
       </c>
       <c r="C10">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -591,7 +589,7 @@
         <v>120</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -604,7 +602,7 @@
         <v>100</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -626,10 +624,10 @@
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="19" x14ac:dyDescent="0.25">
@@ -637,10 +635,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="2" t="s">
@@ -648,132 +646,124 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="9">
-        <f>Score!A6/$C$2</f>
-        <v>2.8571428571428572</v>
-      </c>
-      <c r="B6" s="9">
+      <c r="A6" s="8">
+        <f>Score!A6*($C$2/10)</f>
+        <v>20</v>
+      </c>
+      <c r="B6" s="8">
         <f>C6*2</f>
-        <v>2.8571428571428572</v>
-      </c>
-      <c r="C6" s="9">
-        <f>Score!C6/$C$2</f>
-        <v>1.4285714285714286</v>
+        <v>20</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="9">
-        <f>Score!A7/$C$2</f>
-        <v>4.2857142857142856</v>
-      </c>
-      <c r="B7" s="9">
+      <c r="A7" s="8">
+        <f>Score!A7*($C$2/10)</f>
+        <v>30</v>
+      </c>
+      <c r="B7" s="8">
         <f>C7*3/8</f>
-        <v>4.2857142857142856</v>
-      </c>
-      <c r="C7" s="9">
-        <f>Score!C7/$C$2</f>
-        <v>11.428571428571429</v>
+        <v>30</v>
+      </c>
+      <c r="C7">
+        <v>80</v>
       </c>
       <c r="E7" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="9">
-        <f>Score!A8/$C$2</f>
-        <v>1.4285714285714286</v>
-      </c>
-      <c r="B8" s="9">
+      <c r="A8" s="8">
+        <f>Score!A8*($C$2/10)</f>
+        <v>10</v>
+      </c>
+      <c r="B8" s="8">
         <f>C8*2/3</f>
-        <v>1.4285714285714286</v>
-      </c>
-      <c r="C8" s="9">
-        <f>Score!C8/$C$2</f>
-        <v>2.1428571428571428</v>
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>15</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="9">
-        <f>Score!A9/$C$2</f>
-        <v>1.4285714285714286</v>
-      </c>
-      <c r="B9" s="9">
-        <f>C9/4</f>
-        <v>1.4285714285714286</v>
-      </c>
-      <c r="C9" s="9">
-        <f>Score!C9/$C$2</f>
-        <v>5.7142857142857144</v>
+      <c r="A9" s="8">
+        <f>Score!A9*($C$2/10)</f>
+        <v>10</v>
+      </c>
+      <c r="B9" s="8">
+        <f>C9/2</f>
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <v>20</v>
       </c>
       <c r="E9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="8">
+        <f>Score!A10*($C$2/10)</f>
+        <v>10</v>
+      </c>
+      <c r="B10" s="8">
+        <f>C10/2</f>
+        <v>10</v>
+      </c>
+      <c r="C10">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="8">
+        <f>Score!A11*($C$2/10)</f>
+        <v>20</v>
+      </c>
+      <c r="B11" s="8">
+        <f>C11/6</f>
+        <v>20</v>
+      </c>
+      <c r="C11">
+        <v>120</v>
+      </c>
+      <c r="E11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="9">
-        <f>Score!A10/$C$2</f>
-        <v>1.4285714285714286</v>
-      </c>
-      <c r="B10" s="9">
-        <f>C10/4</f>
-        <v>1.4285714285714286</v>
-      </c>
-      <c r="C10" s="9">
-        <f>Score!C10/$C$2</f>
-        <v>5.7142857142857144</v>
-      </c>
-      <c r="E10" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="8">
+        <f>SUM(A6:A11)</f>
+        <v>100</v>
+      </c>
+      <c r="B13" s="8">
+        <f>SUM(B6:B11)</f>
+        <v>100</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="E13" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="9">
-        <f>Score!A11/$C$2</f>
-        <v>2.8571428571428572</v>
-      </c>
-      <c r="B11" s="9">
-        <f>C11/6</f>
-        <v>2.8571428571428572</v>
-      </c>
-      <c r="C11" s="9">
-        <f>Score!C11/$C$2</f>
-        <v>17.142857142857142</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="9">
-        <f>SUM(A6:A11)</f>
-        <v>14.285714285714286</v>
-      </c>
-      <c r="B13" s="9">
-        <f>SUM(B6:B11)</f>
-        <v>14.285714285714286</v>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="E13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="9">
-        <f>100/C2</f>
-        <v>14.285714285714286</v>
-      </c>
+      <c r="F13" s="10">
+        <f>B13/A13</f>
+        <v>1</v>
+      </c>
+      <c r="G13" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
